--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -1420,7 +1420,7 @@
         <v>24</v>
       </c>
       <c r="G5" s="1">
-        <v>5500</v>
+        <v>2000</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>25</v>
@@ -1472,7 +1472,7 @@
         <v>31</v>
       </c>
       <c r="G7" s="1">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>25</v>
@@ -1607,13 +1607,19 @@
     <row r="19" spans="8:8">
       <c r="H19"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="5:8">
+      <c r="E20" s="1"/>
+      <c r="F20" s="3"/>
       <c r="H20"/>
     </row>
-    <row r="21" spans="8:8">
+    <row r="21" spans="5:8">
+      <c r="E21" s="1"/>
+      <c r="F21" s="3"/>
       <c r="H21"/>
     </row>
-    <row r="22" spans="8:8">
+    <row r="22" spans="5:8">
+      <c r="E22" s="1"/>
+      <c r="F22" s="3"/>
       <c r="H22"/>
     </row>
     <row r="23" spans="8:8">

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -222,7 +222,7 @@
     <t>1022501_3</t>
   </si>
   <si>
-    <t>1_10_0|10_999999_10</t>
+    <t>1_10_0|10_999999_5000</t>
   </si>
   <si>
     <t>0_2_600_1200_5000|2_12_1800_3600_1000|12_24_1800_3600_2000</t>
@@ -234,7 +234,7 @@
     <t>1022501_8</t>
   </si>
   <si>
-    <t>1_50_0|50_999999_10</t>
+    <t>1_50_0|50_999999_5000</t>
   </si>
   <si>
     <t>金</t>
@@ -243,7 +243,7 @@
     <t>1022501_15</t>
   </si>
   <si>
-    <t>1_100_0|10_999999_10</t>
+    <t>1_100_0|10_999999_5000</t>
   </si>
   <si>
     <t>阶段奖励</t>
@@ -1609,17 +1609,14 @@
     </row>
     <row r="20" spans="5:8">
       <c r="E20" s="1"/>
-      <c r="F20" s="3"/>
       <c r="H20"/>
     </row>
     <row r="21" spans="5:8">
       <c r="E21" s="1"/>
-      <c r="F21" s="3"/>
       <c r="H21"/>
     </row>
     <row r="22" spans="5:8">
       <c r="E22" s="1"/>
-      <c r="F22" s="3"/>
       <c r="H22"/>
     </row>
     <row r="23" spans="8:8">

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
   <si>
     <t>序列ID</t>
   </si>
@@ -222,10 +222,10 @@
     <t>1022501_3</t>
   </si>
   <si>
-    <t>1_10_0|10_999999_5000</t>
-  </si>
-  <si>
-    <t>0_2_600_1200_5000|2_12_1800_3600_1000|12_24_1800_3600_2000</t>
+    <t>1_15_0|15_999999_150</t>
+  </si>
+  <si>
+    <t>0_12_1200_3600_1180|12_24_600_1800_2360</t>
   </si>
   <si>
     <t>银</t>
@@ -234,7 +234,10 @@
     <t>1022501_8</t>
   </si>
   <si>
-    <t>1_50_0|50_999999_5000</t>
+    <t>1_5_0|5_999999_350</t>
+  </si>
+  <si>
+    <t>0_12_1200_4800_546|12_24_600_2400_1092</t>
   </si>
   <si>
     <t>金</t>
@@ -243,7 +246,10 @@
     <t>1022501_15</t>
   </si>
   <si>
-    <t>1_100_0|10_999999_5000</t>
+    <t>1_2_0|2_999999_500</t>
+  </si>
+  <si>
+    <t>0_12_1200_7200_382|12_24_600_3600_764</t>
   </si>
   <si>
     <t>阶段奖励</t>
@@ -255,10 +261,10 @@
     <t>1022501_10</t>
   </si>
   <si>
-    <t>1022501_20</t>
-  </si>
-  <si>
-    <t>1022501_30</t>
+    <t>1022501_25</t>
+  </si>
+  <si>
+    <t>1022501_35</t>
   </si>
 </sst>
 </file>
@@ -1446,10 +1452,10 @@
         <v>28</v>
       </c>
       <c r="G6" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:8">
@@ -1457,7 +1463,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
@@ -1466,16 +1472,16 @@
         <v>600000</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:10">
@@ -1483,7 +1489,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -1492,10 +1498,10 @@
       <c r="E8" s="2"/>
       <c r="H8" s="6"/>
       <c r="I8" s="1">
-        <v>100000</v>
+        <v>900000</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:10">
@@ -1503,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -1512,10 +1518,10 @@
       <c r="E9" s="2"/>
       <c r="H9" s="6"/>
       <c r="I9" s="1">
-        <v>500000</v>
+        <v>9000000</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:10">
@@ -1523,7 +1529,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -1532,10 +1538,10 @@
       <c r="E10" s="2"/>
       <c r="H10" s="6"/>
       <c r="I10" s="1">
-        <v>1000000</v>
+        <v>27000000</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:10">
@@ -1543,7 +1549,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1552,10 +1558,10 @@
       <c r="E11" s="2"/>
       <c r="H11" s="6"/>
       <c r="I11" s="1">
-        <v>5000000</v>
+        <v>45000000</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:10">
@@ -1563,7 +1569,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -1572,10 +1578,10 @@
       <c r="E12" s="2"/>
       <c r="H12" s="6"/>
       <c r="I12" s="1">
-        <v>10000000</v>
+        <v>90000000</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:10">

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -1420,7 +1420,7 @@
         <v>24</v>
       </c>
       <c r="G5" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>25</v>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -222,7 +222,7 @@
     <t>1022501_3</t>
   </si>
   <si>
-    <t>1_15_0|15_999999_150</t>
+    <t>1_6_0|6_999999_400</t>
   </si>
   <si>
     <t>0_12_1200_3600_1180|12_24_600_1800_2360</t>
@@ -234,7 +234,7 @@
     <t>1022501_8</t>
   </si>
   <si>
-    <t>1_5_0|5_999999_350</t>
+    <t>1_3_0|3_999999_500</t>
   </si>
   <si>
     <t>0_12_1200_4800_546|12_24_600_2400_1092</t>
@@ -246,7 +246,7 @@
     <t>1022501_15</t>
   </si>
   <si>
-    <t>1_2_0|2_999999_500</t>
+    <t>1_1_0|1_999999_600</t>
   </si>
   <si>
     <t>0_12_1200_7200_382|12_24_600_3600_764</t>
@@ -1406,7 +1406,7 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
+    <row r="5" s="1" customFormat="1" spans="1:10">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
+    <row r="6" s="1" customFormat="1" spans="1:10">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:8">
+    <row r="7" s="2" customFormat="1" spans="1:10">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1594,23 +1594,23 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="8:8">
+    <row r="14" spans="1:10">
       <c r="H14"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:10">
       <c r="A15" s="7"/>
       <c r="H15"/>
     </row>
-    <row r="16" spans="8:8">
+    <row r="16" spans="1:10">
       <c r="H16"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="5:8">
       <c r="H17"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="5:8">
       <c r="H18"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="5:8">
       <c r="H19"/>
     </row>
     <row r="20" spans="5:8">
@@ -1625,16 +1625,16 @@
       <c r="E22" s="1"/>
       <c r="H22"/>
     </row>
-    <row r="23" spans="8:8">
+    <row r="23" spans="5:8">
       <c r="H23"/>
     </row>
-    <row r="24" spans="8:8">
+    <row r="24" spans="5:8">
       <c r="H24"/>
     </row>
-    <row r="25" spans="8:8">
+    <row r="25" spans="5:8">
       <c r="H25"/>
     </row>
-    <row r="26" spans="8:8">
+    <row r="26" spans="5:8">
       <c r="H26"/>
     </row>
   </sheetData>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
   <si>
     <t>序列ID</t>
   </si>
@@ -252,19 +252,52 @@
     <t>0_12_1200_7200_382|12_24_600_3600_764</t>
   </si>
   <si>
-    <t>阶段奖励</t>
+    <t>阶段奖励1</t>
   </si>
   <si>
     <t>1022501_5</t>
   </si>
   <si>
+    <t>阶段奖励2</t>
+  </si>
+  <si>
     <t>1022501_10</t>
   </si>
   <si>
+    <t>阶段奖励3</t>
+  </si>
+  <si>
+    <t>阶段奖励4</t>
+  </si>
+  <si>
     <t>1022501_25</t>
   </si>
   <si>
+    <t>阶段奖励5</t>
+  </si>
+  <si>
     <t>1022501_35</t>
+  </si>
+  <si>
+    <t>阶段奖励6</t>
+  </si>
+  <si>
+    <t>阶段奖励7</t>
+  </si>
+  <si>
+    <t>阶段奖励8</t>
+  </si>
+  <si>
+    <t>阶段奖励9</t>
+  </si>
+  <si>
+    <t>阶段奖励10</t>
+  </si>
+  <si>
+    <t>阶段奖励11</t>
+  </si>
+  <si>
+    <t>阶段奖励12</t>
   </si>
 </sst>
 </file>
@@ -915,7 +948,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -935,9 +968,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1509,7 +1539,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -1521,7 +1551,7 @@
         <v>9000000</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:10">
@@ -1529,7 +1559,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -1549,7 +1579,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1561,7 +1591,7 @@
         <v>45000000</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:10">
@@ -1569,7 +1599,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -1581,60 +1611,165 @@
         <v>90000000</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:10">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
       <c r="H13" s="6"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="H14"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="7"/>
-      <c r="H15"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="H16"/>
-    </row>
-    <row r="17" spans="5:8">
-      <c r="H17"/>
-    </row>
-    <row r="18" spans="5:8">
-      <c r="H18"/>
-    </row>
-    <row r="19" spans="5:8">
-      <c r="H19"/>
-    </row>
-    <row r="20" spans="5:8">
+      <c r="I13" s="1">
+        <v>90000000</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:10">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="1">
+        <v>90000000</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:10">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="1">
+        <v>90000000</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:10">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="1">
+        <v>90000000</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:10">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="1">
+        <v>90000000</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:10">
+      <c r="A18" s="1">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="1">
+        <v>90000000</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:10">
+      <c r="A19" s="1">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="1">
+        <v>90000000</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="E20" s="1"/>
       <c r="H20"/>
     </row>
-    <row r="21" spans="5:8">
+    <row r="21" spans="1:10">
       <c r="E21" s="1"/>
       <c r="H21"/>
     </row>
-    <row r="22" spans="5:8">
+    <row r="22" spans="1:10">
       <c r="E22" s="1"/>
       <c r="H22"/>
     </row>
-    <row r="23" spans="5:8">
+    <row r="23" spans="1:10">
       <c r="H23"/>
     </row>
-    <row r="24" spans="5:8">
+    <row r="24" spans="1:10">
       <c r="H24"/>
     </row>
-    <row r="25" spans="5:8">
+    <row r="25" spans="1:10">
       <c r="H25"/>
     </row>
-    <row r="26" spans="5:8">
+    <row r="26" spans="1:10">
       <c r="H26"/>
     </row>
   </sheetData>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
   <si>
     <t>序列ID</t>
   </si>
@@ -222,10 +222,10 @@
     <t>1022501_3</t>
   </si>
   <si>
-    <t>1_6_0|6_999999_400</t>
-  </si>
-  <si>
-    <t>0_12_1200_3600_1180|12_24_600_1800_2360</t>
+    <t>1_0_0|0_999999_2000</t>
+  </si>
+  <si>
+    <t>0_12_1200_3600_1180|12_24_600_3600_2360</t>
   </si>
   <si>
     <t>银</t>
@@ -234,10 +234,10 @@
     <t>1022501_8</t>
   </si>
   <si>
-    <t>1_3_0|3_999999_500</t>
-  </si>
-  <si>
-    <t>0_12_1200_4800_546|12_24_600_2400_1092</t>
+    <t>1_1_0|1_999999_800</t>
+  </si>
+  <si>
+    <t>0_12_1200_4800_546|12_24_600_4800_1092</t>
   </si>
   <si>
     <t>金</t>
@@ -246,10 +246,10 @@
     <t>1022501_15</t>
   </si>
   <si>
-    <t>1_1_0|1_999999_600</t>
-  </si>
-  <si>
-    <t>0_12_1200_7200_382|12_24_600_3600_764</t>
+    <t>1_1_0|1_999999_350</t>
+  </si>
+  <si>
+    <t>0_12_1200_7200_382|12_24_600_7200_764</t>
   </si>
   <si>
     <t>阶段奖励1</t>
@@ -270,34 +270,40 @@
     <t>阶段奖励4</t>
   </si>
   <si>
+    <t>阶段奖励5</t>
+  </si>
+  <si>
+    <t>阶段奖励6</t>
+  </si>
+  <si>
+    <t>1022501_20</t>
+  </si>
+  <si>
+    <t>阶段奖励7</t>
+  </si>
+  <si>
+    <t>阶段奖励8</t>
+  </si>
+  <si>
     <t>1022501_25</t>
   </si>
   <si>
-    <t>阶段奖励5</t>
-  </si>
-  <si>
-    <t>1022501_35</t>
-  </si>
-  <si>
-    <t>阶段奖励6</t>
-  </si>
-  <si>
-    <t>阶段奖励7</t>
-  </si>
-  <si>
-    <t>阶段奖励8</t>
-  </si>
-  <si>
     <t>阶段奖励9</t>
   </si>
   <si>
     <t>阶段奖励10</t>
   </si>
   <si>
+    <t>1022501_30</t>
+  </si>
+  <si>
     <t>阶段奖励11</t>
   </si>
   <si>
     <t>阶段奖励12</t>
+  </si>
+  <si>
+    <t>1022501_40</t>
   </si>
 </sst>
 </file>
@@ -1447,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -1456,7 +1462,7 @@
         <v>24</v>
       </c>
       <c r="G5" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>25</v>
@@ -1473,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>27</v>
@@ -1482,7 +1488,7 @@
         <v>28</v>
       </c>
       <c r="G6" s="1">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>29</v>
@@ -1499,7 +1505,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>600000</v>
+        <v>890000</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>31</v>
@@ -1508,7 +1514,7 @@
         <v>32</v>
       </c>
       <c r="G7" s="1">
-        <v>6000</v>
+        <v>8900</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>33</v>
@@ -1571,7 +1577,7 @@
         <v>27000000</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:10">
@@ -1591,7 +1597,7 @@
         <v>45000000</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:10">
@@ -1599,7 +1605,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -1611,7 +1617,7 @@
         <v>90000000</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:10">
@@ -1619,7 +1625,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -1628,7 +1634,8 @@
       <c r="E13" s="2"/>
       <c r="H13" s="6"/>
       <c r="I13" s="1">
-        <v>90000000</v>
+        <f>I12+$I$12</f>
+        <v>180000000</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>42</v>
@@ -1639,7 +1646,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1647,7 +1654,8 @@
       <c r="D14" s="1"/>
       <c r="H14" s="6"/>
       <c r="I14" s="1">
-        <v>90000000</v>
+        <f t="shared" ref="I14:I19" si="0">I13+$I$12</f>
+        <v>270000000</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>42</v>
@@ -1658,7 +1666,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -1666,10 +1674,11 @@
       <c r="D15" s="1"/>
       <c r="H15" s="6"/>
       <c r="I15" s="1">
-        <v>90000000</v>
+        <f t="shared" si="0"/>
+        <v>360000000</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:10">
@@ -1685,10 +1694,11 @@
       <c r="D16" s="1"/>
       <c r="H16" s="6"/>
       <c r="I16" s="1">
-        <v>90000000</v>
+        <f t="shared" si="0"/>
+        <v>450000000</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:10">
@@ -1704,10 +1714,11 @@
       <c r="D17" s="1"/>
       <c r="H17" s="6"/>
       <c r="I17" s="1">
-        <v>90000000</v>
+        <f t="shared" si="0"/>
+        <v>540000000</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:10">
@@ -1715,7 +1726,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -1723,10 +1734,11 @@
       <c r="D18" s="1"/>
       <c r="H18" s="6"/>
       <c r="I18" s="1">
-        <v>90000000</v>
+        <f t="shared" si="0"/>
+        <v>630000000</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:10">
@@ -1734,7 +1746,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -1742,10 +1754,11 @@
       <c r="D19" s="1"/>
       <c r="H19" s="6"/>
       <c r="I19" s="1">
-        <v>90000000</v>
+        <f t="shared" si="0"/>
+        <v>720000000</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:10">

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -1453,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>100000</v>
+        <v>180000</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>27</v>
@@ -1505,7 +1505,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>890000</v>
+        <v>800000</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>31</v>
@@ -1534,7 +1534,7 @@
       <c r="E8" s="2"/>
       <c r="H8" s="6"/>
       <c r="I8" s="1">
-        <v>900000</v>
+        <v>1200000</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>35</v>
@@ -1554,7 +1554,7 @@
       <c r="E9" s="2"/>
       <c r="H9" s="6"/>
       <c r="I9" s="1">
-        <v>9000000</v>
+        <v>6400000</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>37</v>
@@ -1574,7 +1574,7 @@
       <c r="E10" s="2"/>
       <c r="H10" s="6"/>
       <c r="I10" s="1">
-        <v>27000000</v>
+        <v>10600000</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>37</v>
@@ -1594,7 +1594,7 @@
       <c r="E11" s="2"/>
       <c r="H11" s="6"/>
       <c r="I11" s="1">
-        <v>45000000</v>
+        <v>16900000</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>31</v>
@@ -1614,7 +1614,7 @@
       <c r="E12" s="2"/>
       <c r="H12" s="6"/>
       <c r="I12" s="1">
-        <v>90000000</v>
+        <v>23200000</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>31</v>
@@ -1634,8 +1634,7 @@
       <c r="E13" s="2"/>
       <c r="H13" s="6"/>
       <c r="I13" s="1">
-        <f>I12+$I$12</f>
-        <v>180000000</v>
+        <v>31600000</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>42</v>
@@ -1654,8 +1653,7 @@
       <c r="D14" s="1"/>
       <c r="H14" s="6"/>
       <c r="I14" s="1">
-        <f t="shared" ref="I14:I19" si="0">I13+$I$12</f>
-        <v>270000000</v>
+        <v>40000000</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>42</v>
@@ -1674,8 +1672,7 @@
       <c r="D15" s="1"/>
       <c r="H15" s="6"/>
       <c r="I15" s="1">
-        <f t="shared" si="0"/>
-        <v>360000000</v>
+        <v>50500000</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>45</v>
@@ -1694,8 +1691,7 @@
       <c r="D16" s="1"/>
       <c r="H16" s="6"/>
       <c r="I16" s="1">
-        <f t="shared" si="0"/>
-        <v>450000000</v>
+        <v>61000000</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>45</v>
@@ -1714,8 +1710,7 @@
       <c r="D17" s="1"/>
       <c r="H17" s="6"/>
       <c r="I17" s="1">
-        <f t="shared" si="0"/>
-        <v>540000000</v>
+        <v>73700000</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>48</v>
@@ -1734,8 +1729,7 @@
       <c r="D18" s="1"/>
       <c r="H18" s="6"/>
       <c r="I18" s="1">
-        <f t="shared" si="0"/>
-        <v>630000000</v>
+        <v>86300000</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>48</v>
@@ -1754,8 +1748,7 @@
       <c r="D19" s="1"/>
       <c r="H19" s="6"/>
       <c r="I19" s="1">
-        <f t="shared" si="0"/>
-        <v>720000000</v>
+        <v>103100000</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>51</v>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -222,7 +222,7 @@
     <t>1022501_3</t>
   </si>
   <si>
-    <t>1_0_0|0_999999_2000</t>
+    <t>1_0_0|0_999999_1200</t>
   </si>
   <si>
     <t>0_12_1200_3600_1180|12_24_600_3600_2360</t>
@@ -246,7 +246,7 @@
     <t>1022501_15</t>
   </si>
   <si>
-    <t>1_1_0|1_999999_350</t>
+    <t>1_1_0|1_999999_400</t>
   </si>
   <si>
     <t>0_12_1200_7200_382|12_24_600_7200_764</t>
@@ -1453,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>23</v>
@@ -1462,7 +1462,7 @@
         <v>24</v>
       </c>
       <c r="G5" s="1">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>25</v>
@@ -1479,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>180000</v>
+        <v>195000</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>27</v>
@@ -1488,7 +1488,7 @@
         <v>28</v>
       </c>
       <c r="G6" s="1">
-        <v>1000</v>
+        <v>1950</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>29</v>
@@ -1505,7 +1505,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>800000</v>
+        <v>765000</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>31</v>
@@ -1514,7 +1514,7 @@
         <v>32</v>
       </c>
       <c r="G7" s="1">
-        <v>8900</v>
+        <v>7650</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>33</v>
@@ -1554,7 +1554,7 @@
       <c r="E9" s="2"/>
       <c r="H9" s="6"/>
       <c r="I9" s="1">
-        <v>6400000</v>
+        <v>3500000</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>37</v>
@@ -1574,7 +1574,7 @@
       <c r="E10" s="2"/>
       <c r="H10" s="6"/>
       <c r="I10" s="1">
-        <v>10600000</v>
+        <v>5800000</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>37</v>
@@ -1594,7 +1594,7 @@
       <c r="E11" s="2"/>
       <c r="H11" s="6"/>
       <c r="I11" s="1">
-        <v>16900000</v>
+        <v>9200000</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>31</v>
@@ -1614,7 +1614,7 @@
       <c r="E12" s="2"/>
       <c r="H12" s="6"/>
       <c r="I12" s="1">
-        <v>23200000</v>
+        <v>12700000</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>31</v>
@@ -1634,7 +1634,7 @@
       <c r="E13" s="2"/>
       <c r="H13" s="6"/>
       <c r="I13" s="1">
-        <v>31600000</v>
+        <v>17300000</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>42</v>
@@ -1653,7 +1653,7 @@
       <c r="D14" s="1"/>
       <c r="H14" s="6"/>
       <c r="I14" s="1">
-        <v>40000000</v>
+        <v>21900000</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>42</v>
@@ -1672,7 +1672,7 @@
       <c r="D15" s="1"/>
       <c r="H15" s="6"/>
       <c r="I15" s="1">
-        <v>50500000</v>
+        <v>27600000</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>45</v>
@@ -1691,7 +1691,7 @@
       <c r="D16" s="1"/>
       <c r="H16" s="6"/>
       <c r="I16" s="1">
-        <v>61000000</v>
+        <v>33400000</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>45</v>
@@ -1710,7 +1710,7 @@
       <c r="D17" s="1"/>
       <c r="H17" s="6"/>
       <c r="I17" s="1">
-        <v>73700000</v>
+        <v>40300000</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>48</v>
@@ -1729,7 +1729,7 @@
       <c r="D18" s="1"/>
       <c r="H18" s="6"/>
       <c r="I18" s="1">
-        <v>86300000</v>
+        <v>47200000</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>48</v>
@@ -1748,7 +1748,7 @@
       <c r="D19" s="1"/>
       <c r="H19" s="6"/>
       <c r="I19" s="1">
-        <v>103100000</v>
+        <v>56400000</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>51</v>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3F9EA3-8470-4F65-83CD-8E27C1BCB35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="3150" yWindow="4185" windowWidth="15660" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -22,17 +28,20 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -54,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -76,7 +85,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -95,11 +126,11 @@
           </rPr>
           <t xml:space="preserve">
 从活动开始后开始计算倒计时，倒计时结束走概率判断是否中奖，接着抽取下一次抽奖倒计时
-服务器时间开始/时_服务器时间结束/时_等待间隔下限/秒_等待间隔上限/秒_中奖概率万分比</t>
+服务器时间开始/时_服务器时间结束/时_等待间隔下限/秒_等待间隔上限/秒_大奖中奖概率万分比_固定金额中奖概率万分比</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -148,7 +179,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
   <si>
     <t>序列ID</t>
   </si>
@@ -171,6 +202,12 @@
     <t>所占总奖池比例万分比</t>
   </si>
   <si>
+    <t>固定金额奖励：次数下限_次数上限（左闭右开）_玩家中奖万分比概率|</t>
+  </si>
+  <si>
+    <t>固定金额奖励</t>
+  </si>
+  <si>
     <t>机器人中奖频率</t>
   </si>
   <si>
@@ -207,6 +244,12 @@
     <t>distribution</t>
   </si>
   <si>
+    <t>weightQuota</t>
+  </si>
+  <si>
+    <t>distributionQuota</t>
+  </si>
+  <si>
     <t>winningFrequency</t>
   </si>
   <si>
@@ -225,6 +268,9 @@
     <t>1_0_0|0_999999_1200</t>
   </si>
   <si>
+    <t>0_999999_1200</t>
+  </si>
+  <si>
     <t>0_12_1200_3600_1180|12_24_600_3600_2360</t>
   </si>
   <si>
@@ -304,19 +350,17 @@
   </si>
   <si>
     <t>1022501_40</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,147 +392,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -502,8 +409,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -512,192 +432,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -705,256 +451,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -970,70 +474,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.799340800195319"/>
+          <bgColor theme="8" tint="0.7993408001953185"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1042,6 +505,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1319,13 +785,13 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="3" customWidth="1"/>
@@ -1335,13 +801,14 @@
     <col min="5" max="5" width="15.375" style="3" customWidth="1"/>
     <col min="6" max="6" width="44.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.25" style="3" customWidth="1"/>
-    <col min="8" max="8" width="61.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14.625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="17.5" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="3"/>
+    <col min="8" max="9" width="44" style="3" customWidth="1"/>
+    <col min="10" max="10" width="61.625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="17.5" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1363,91 +830,109 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="L2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="I3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -1456,24 +941,30 @@
         <v>40000</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G5" s="1">
         <v>400</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:10">
+        <v>29</v>
+      </c>
+      <c r="I5" s="7">
+        <v>700000</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1">
         <v>2</v>
@@ -1482,10 +973,10 @@
         <v>195000</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G6" s="1">
         <v>1950</v>
@@ -1493,13 +984,19 @@
       <c r="H6" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:10">
+      <c r="I6" s="7">
+        <v>700000</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1">
       <c r="A7" s="1">
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
@@ -1508,284 +1005,284 @@
         <v>765000</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1">
         <v>7650</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:10">
+        <v>29</v>
+      </c>
+      <c r="I7" s="7">
+        <v>700000</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="2"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="1">
+      <c r="J8" s="8"/>
+      <c r="K8" s="1">
         <v>1200000</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:10">
+      <c r="L8" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="2"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="1">
+      <c r="J9" s="8"/>
+      <c r="K9" s="1">
         <v>3500000</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:10">
+      <c r="L9" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1">
       <c r="A10" s="1">
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="1">
+      <c r="J10" s="8"/>
+      <c r="K10" s="1">
         <v>5800000</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:10">
+      <c r="L10" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="1">
+      <c r="J11" s="8"/>
+      <c r="K11" s="1">
         <v>9200000</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:10">
+      <c r="L11" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="1">
+      <c r="J12" s="8"/>
+      <c r="K12" s="1">
         <v>12700000</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:10">
+      <c r="L12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="1">
+      <c r="J13" s="8"/>
+      <c r="K13" s="1">
         <v>17300000</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:10">
+      <c r="L13" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1">
       <c r="A14" s="1">
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="1">
+      <c r="J14" s="8"/>
+      <c r="K14" s="1">
         <v>21900000</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:10">
+      <c r="L14" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1">
       <c r="A15" s="1">
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="1">
+      <c r="J15" s="8"/>
+      <c r="K15" s="1">
         <v>27600000</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:10">
+      <c r="L15" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1">
       <c r="A16" s="1">
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="1">
+      <c r="J16" s="8"/>
+      <c r="K16" s="1">
         <v>33400000</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:10">
+      <c r="L16" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="2" customFormat="1">
       <c r="A17" s="1">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="1">
+      <c r="J17" s="8"/>
+      <c r="K17" s="1">
         <v>40300000</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:10">
+      <c r="L17" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1">
       <c r="A18" s="1">
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="1">
+      <c r="J18" s="8"/>
+      <c r="K18" s="1">
         <v>47200000</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:10">
+      <c r="L18" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1">
       <c r="A19" s="1">
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="1"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="1">
+      <c r="J19" s="8"/>
+      <c r="K19" s="1">
         <v>56400000</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="L19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="E20" s="1"/>
-      <c r="H20"/>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="1:12">
       <c r="E21" s="1"/>
-      <c r="H21"/>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="1:12">
       <c r="E22" s="1"/>
-      <c r="H22"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="H23"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="H24"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="H25"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="H26"/>
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="J23"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="J24"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="J25"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="J26"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2">
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="L2">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B2,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3F9EA3-8470-4F65-83CD-8E27C1BCB35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="4185" windowWidth="15660" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -28,20 +22,17 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -63,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +76,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -152,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -179,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
   <si>
     <t>序列ID</t>
   </si>
@@ -350,17 +341,19 @@
   </si>
   <si>
     <t>1022501_40</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,10 +385,147 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -409,21 +539,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,7 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,8 +559,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -451,14 +748,256 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -484,19 +1023,64 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
@@ -505,9 +1089,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -785,12 +1366,12 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -801,7 +1382,8 @@
     <col min="5" max="5" width="15.375" style="3" customWidth="1"/>
     <col min="6" max="6" width="44.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.25" style="3" customWidth="1"/>
-    <col min="8" max="9" width="44" style="3" customWidth="1"/>
+    <col min="8" max="8" width="44" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.375" style="3" customWidth="1"/>
     <col min="10" max="10" width="61.625" style="3" customWidth="1"/>
     <col min="11" max="11" width="14.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="17.5" style="3" customWidth="1"/>
@@ -869,8 +1451,8 @@
       <c r="H2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>57</v>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>14</v>
@@ -927,7 +1509,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    <row r="5" s="1" customFormat="1" spans="1:12">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -959,7 +1541,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1">
+    <row r="6" s="1" customFormat="1" spans="1:12">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -991,7 +1573,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
+    <row r="7" s="2" customFormat="1" spans="1:12">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1023,7 +1605,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
+    <row r="8" s="2" customFormat="1" spans="1:12">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1034,6 +1616,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1"/>
+      <c r="E8" s="2"/>
       <c r="J8" s="8"/>
       <c r="K8" s="1">
         <v>1200000</v>
@@ -1042,7 +1625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
+    <row r="9" s="2" customFormat="1" spans="1:12">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1053,6 +1636,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1"/>
+      <c r="E9" s="2"/>
       <c r="J9" s="8"/>
       <c r="K9" s="1">
         <v>3500000</v>
@@ -1061,7 +1645,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1">
+    <row r="10" s="2" customFormat="1" spans="1:12">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1072,6 +1656,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1"/>
+      <c r="E10" s="2"/>
       <c r="J10" s="8"/>
       <c r="K10" s="1">
         <v>5800000</v>
@@ -1080,7 +1665,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1">
+    <row r="11" s="2" customFormat="1" spans="1:12">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1091,6 +1676,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1"/>
+      <c r="E11" s="2"/>
       <c r="J11" s="8"/>
       <c r="K11" s="1">
         <v>9200000</v>
@@ -1099,7 +1685,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1">
+    <row r="12" s="2" customFormat="1" spans="1:12">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1110,6 +1696,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="1"/>
+      <c r="E12" s="2"/>
       <c r="J12" s="8"/>
       <c r="K12" s="1">
         <v>12700000</v>
@@ -1118,7 +1705,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1">
+    <row r="13" s="2" customFormat="1" spans="1:12">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1129,6 +1716,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="1"/>
+      <c r="E13" s="2"/>
       <c r="J13" s="8"/>
       <c r="K13" s="1">
         <v>17300000</v>
@@ -1137,7 +1725,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1">
+    <row r="14" s="2" customFormat="1" spans="1:12">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1156,7 +1744,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1">
+    <row r="15" s="2" customFormat="1" spans="1:12">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1175,7 +1763,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1">
+    <row r="16" s="2" customFormat="1" spans="1:12">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1194,7 +1782,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="2" customFormat="1">
+    <row r="17" s="2" customFormat="1" spans="1:12">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1213,7 +1801,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="2" customFormat="1">
+    <row r="18" s="2" customFormat="1" spans="1:12">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1232,7 +1820,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="2" customFormat="1">
+    <row r="19" s="2" customFormat="1" spans="1:12">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1276,13 +1864,13 @@
       <c r="J26"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="L2">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B2,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3F9EA3-8470-4F65-83CD-8E27C1BCB35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="4185" windowWidth="15660" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -28,20 +22,17 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -63,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +76,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -152,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -179,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
   <si>
     <t>序列ID</t>
   </si>
@@ -350,17 +341,19 @@
   </si>
   <si>
     <t>1022501_40</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,11 +385,153 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -404,26 +539,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,7 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,8 +559,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -451,14 +748,256 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -484,19 +1023,64 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.7993408001953185"/>
+          <bgColor theme="8" tint="0.799340800195319"/>
         </patternFill>
       </fill>
     </dxf>
@@ -505,9 +1089,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -785,12 +1366,12 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -801,7 +1382,8 @@
     <col min="5" max="5" width="15.375" style="3" customWidth="1"/>
     <col min="6" max="6" width="44.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.25" style="3" customWidth="1"/>
-    <col min="8" max="9" width="44" style="3" customWidth="1"/>
+    <col min="8" max="8" width="44" style="3" customWidth="1"/>
+    <col min="9" max="9" width="20.375" style="3" customWidth="1"/>
     <col min="10" max="10" width="61.625" style="3" customWidth="1"/>
     <col min="11" max="11" width="14.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="17.5" style="3" customWidth="1"/>
@@ -869,8 +1451,8 @@
       <c r="H2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>57</v>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>14</v>
@@ -927,7 +1509,7 @@
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1">
+    <row r="5" s="1" customFormat="1" spans="1:12">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -959,7 +1541,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1">
+    <row r="6" s="1" customFormat="1" spans="1:12">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -991,7 +1573,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1">
+    <row r="7" s="2" customFormat="1" spans="1:12">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1023,7 +1605,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1">
+    <row r="8" s="2" customFormat="1" spans="1:12">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1034,6 +1616,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1"/>
+      <c r="E8" s="2"/>
       <c r="J8" s="8"/>
       <c r="K8" s="1">
         <v>1200000</v>
@@ -1042,7 +1625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1">
+    <row r="9" s="2" customFormat="1" spans="1:12">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1053,6 +1636,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1"/>
+      <c r="E9" s="2"/>
       <c r="J9" s="8"/>
       <c r="K9" s="1">
         <v>3500000</v>
@@ -1061,7 +1645,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1">
+    <row r="10" s="2" customFormat="1" spans="1:12">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1072,6 +1656,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1"/>
+      <c r="E10" s="2"/>
       <c r="J10" s="8"/>
       <c r="K10" s="1">
         <v>5800000</v>
@@ -1080,7 +1665,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1">
+    <row r="11" s="2" customFormat="1" spans="1:12">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1091,6 +1676,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1"/>
+      <c r="E11" s="2"/>
       <c r="J11" s="8"/>
       <c r="K11" s="1">
         <v>9200000</v>
@@ -1099,7 +1685,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1">
+    <row r="12" s="2" customFormat="1" spans="1:12">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1110,6 +1696,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="1"/>
+      <c r="E12" s="2"/>
       <c r="J12" s="8"/>
       <c r="K12" s="1">
         <v>12700000</v>
@@ -1118,7 +1705,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1">
+    <row r="13" s="2" customFormat="1" spans="1:12">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1129,6 +1716,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="1"/>
+      <c r="E13" s="2"/>
       <c r="J13" s="8"/>
       <c r="K13" s="1">
         <v>17300000</v>
@@ -1137,7 +1725,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1">
+    <row r="14" s="2" customFormat="1" spans="1:12">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1156,7 +1744,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1">
+    <row r="15" s="2" customFormat="1" spans="1:12">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1175,7 +1763,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1">
+    <row r="16" s="2" customFormat="1" spans="1:12">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1194,7 +1782,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="2" customFormat="1">
+    <row r="17" s="2" customFormat="1" spans="1:12">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1213,7 +1801,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="2" customFormat="1">
+    <row r="18" s="2" customFormat="1" spans="1:12">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1232,7 +1820,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="2" customFormat="1">
+    <row r="19" s="2" customFormat="1" spans="1:12">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1276,13 +1864,13 @@
       <c r="J26"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="L2">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B2,2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
   <si>
     <t>序列ID</t>
   </si>
@@ -256,10 +256,10 @@
     <t>1022501_3</t>
   </si>
   <si>
-    <t>1_0_0|0_999999_1200</t>
-  </si>
-  <si>
-    <t>0_999999_1200</t>
+    <t>1_50_0|50_999999_280</t>
+  </si>
+  <si>
+    <t>0_999999_1500</t>
   </si>
   <si>
     <t>0_12_1200_3600_1180|12_24_600_3600_2360</t>
@@ -271,7 +271,10 @@
     <t>1022501_8</t>
   </si>
   <si>
-    <t>1_1_0|1_999999_800</t>
+    <t>1_12_0|12_999999_150</t>
+  </si>
+  <si>
+    <t>0_999999_1000</t>
   </si>
   <si>
     <t>0_12_1200_4800_546|12_24_600_4800_1092</t>
@@ -283,7 +286,10 @@
     <t>1022501_15</t>
   </si>
   <si>
-    <t>1_1_0|1_999999_400</t>
+    <t>1_4_0|4_999999_50</t>
+  </si>
+  <si>
+    <t>0_999999_500</t>
   </si>
   <si>
     <t>0_12_1200_7200_382|12_24_600_7200_764</t>
@@ -313,34 +319,25 @@
     <t>阶段奖励6</t>
   </si>
   <si>
+    <t>阶段奖励7</t>
+  </si>
+  <si>
+    <t>阶段奖励8</t>
+  </si>
+  <si>
     <t>1022501_20</t>
   </si>
   <si>
-    <t>阶段奖励7</t>
-  </si>
-  <si>
-    <t>阶段奖励8</t>
-  </si>
-  <si>
-    <t>1022501_25</t>
-  </si>
-  <si>
     <t>阶段奖励9</t>
   </si>
   <si>
     <t>阶段奖励10</t>
   </si>
   <si>
-    <t>1022501_30</t>
-  </si>
-  <si>
     <t>阶段奖励11</t>
   </si>
   <si>
     <t>阶段奖励12</t>
-  </si>
-  <si>
-    <t>1022501_40</t>
   </si>
 </sst>
 </file>
@@ -529,12 +526,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1520,7 +1517,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>40000</v>
+        <v>260000</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>27</v>
@@ -1535,7 +1532,7 @@
         <v>29</v>
       </c>
       <c r="I5" s="7">
-        <v>700000</v>
+        <v>500</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>30</v>
@@ -1552,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>195000</v>
+        <v>520000</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>32</v>
@@ -1564,13 +1561,13 @@
         <v>1950</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I6" s="7">
-        <v>700000</v>
+        <v>2000</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:12">
@@ -1578,31 +1575,31 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>765000</v>
+        <v>1820000</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="1">
         <v>7650</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I7" s="7">
-        <v>700000</v>
+        <v>25000</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:12">
@@ -1610,7 +1607,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -1619,10 +1616,10 @@
       <c r="E8" s="2"/>
       <c r="J8" s="8"/>
       <c r="K8" s="1">
-        <v>1200000</v>
+        <v>24700000</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:12">
@@ -1630,7 +1627,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -1639,10 +1636,10 @@
       <c r="E9" s="2"/>
       <c r="J9" s="8"/>
       <c r="K9" s="1">
-        <v>3500000</v>
+        <v>74100000</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:12">
@@ -1650,7 +1647,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -1659,10 +1656,10 @@
       <c r="E10" s="2"/>
       <c r="J10" s="8"/>
       <c r="K10" s="1">
-        <v>5800000</v>
+        <v>123500000</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:12">
@@ -1670,7 +1667,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1679,10 +1676,10 @@
       <c r="E11" s="2"/>
       <c r="J11" s="8"/>
       <c r="K11" s="1">
-        <v>9200000</v>
+        <v>197600000</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:12">
@@ -1690,7 +1687,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -1699,10 +1696,10 @@
       <c r="E12" s="2"/>
       <c r="J12" s="8"/>
       <c r="K12" s="1">
-        <v>12700000</v>
+        <v>271700000</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:12">
@@ -1710,7 +1707,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -1719,10 +1716,10 @@
       <c r="E13" s="2"/>
       <c r="J13" s="8"/>
       <c r="K13" s="1">
-        <v>17300000</v>
+        <v>345800000</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:12">
@@ -1730,7 +1727,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1738,10 +1735,10 @@
       <c r="D14" s="1"/>
       <c r="J14" s="8"/>
       <c r="K14" s="1">
-        <v>21900000</v>
+        <v>419800000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:12">
@@ -1749,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -1757,10 +1754,10 @@
       <c r="D15" s="1"/>
       <c r="J15" s="8"/>
       <c r="K15" s="1">
-        <v>27600000</v>
+        <v>518600000</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:12">
@@ -1768,7 +1765,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" s="1">
         <v>4</v>
@@ -1776,10 +1773,10 @@
       <c r="D16" s="1"/>
       <c r="J16" s="8"/>
       <c r="K16" s="1">
-        <v>33400000</v>
+        <v>617400000</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:12">
@@ -1787,7 +1784,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
@@ -1795,10 +1792,10 @@
       <c r="D17" s="1"/>
       <c r="J17" s="8"/>
       <c r="K17" s="1">
-        <v>40300000</v>
+        <v>716200000</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:12">
@@ -1814,10 +1811,10 @@
       <c r="D18" s="1"/>
       <c r="J18" s="8"/>
       <c r="K18" s="1">
-        <v>47200000</v>
+        <v>814900000</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:12">
@@ -1833,10 +1830,10 @@
       <c r="D19" s="1"/>
       <c r="J19" s="8"/>
       <c r="K19" s="1">
-        <v>56400000</v>
+        <v>913700000</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:12">

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -1526,7 +1526,7 @@
         <v>28</v>
       </c>
       <c r="G5" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>29</v>
@@ -1558,7 +1558,7 @@
         <v>33</v>
       </c>
       <c r="G6" s="1">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>34</v>
@@ -1590,7 +1590,7 @@
         <v>38</v>
       </c>
       <c r="G7" s="1">
-        <v>7650</v>
+        <v>7000</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>39</v>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
   <si>
     <t>序列ID</t>
   </si>
@@ -256,10 +256,10 @@
     <t>1022501_3</t>
   </si>
   <si>
-    <t>1_0_0|0_999999_1200</t>
-  </si>
-  <si>
-    <t>0_999999_1200</t>
+    <t>1_50_0|50_999999_280</t>
+  </si>
+  <si>
+    <t>0_999999_1500</t>
   </si>
   <si>
     <t>0_12_1200_3600_1180|12_24_600_3600_2360</t>
@@ -271,7 +271,10 @@
     <t>1022501_8</t>
   </si>
   <si>
-    <t>1_1_0|1_999999_800</t>
+    <t>1_12_0|12_999999_150</t>
+  </si>
+  <si>
+    <t>0_999999_1000</t>
   </si>
   <si>
     <t>0_12_1200_4800_546|12_24_600_4800_1092</t>
@@ -283,7 +286,10 @@
     <t>1022501_15</t>
   </si>
   <si>
-    <t>1_1_0|1_999999_400</t>
+    <t>1_4_0|4_999999_50</t>
+  </si>
+  <si>
+    <t>0_999999_500</t>
   </si>
   <si>
     <t>0_12_1200_7200_382|12_24_600_7200_764</t>
@@ -313,34 +319,25 @@
     <t>阶段奖励6</t>
   </si>
   <si>
+    <t>阶段奖励7</t>
+  </si>
+  <si>
+    <t>阶段奖励8</t>
+  </si>
+  <si>
     <t>1022501_20</t>
   </si>
   <si>
-    <t>阶段奖励7</t>
-  </si>
-  <si>
-    <t>阶段奖励8</t>
-  </si>
-  <si>
-    <t>1022501_25</t>
-  </si>
-  <si>
     <t>阶段奖励9</t>
   </si>
   <si>
     <t>阶段奖励10</t>
   </si>
   <si>
-    <t>1022501_30</t>
-  </si>
-  <si>
     <t>阶段奖励11</t>
   </si>
   <si>
     <t>阶段奖励12</t>
-  </si>
-  <si>
-    <t>1022501_40</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1380,7 @@
     <col min="6" max="6" width="44.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="44" style="3" customWidth="1"/>
-    <col min="9" max="9" width="18.375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="20.375" style="3" customWidth="1"/>
     <col min="10" max="10" width="61.625" style="3" customWidth="1"/>
     <col min="11" max="11" width="14.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="17.5" style="3" customWidth="1"/>
@@ -1520,7 +1517,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>40000</v>
+        <v>260000</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>27</v>
@@ -1529,13 +1526,13 @@
         <v>28</v>
       </c>
       <c r="G5" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="I5" s="7">
-        <v>700000</v>
+        <v>500</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>30</v>
@@ -1552,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>195000</v>
+        <v>520000</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>32</v>
@@ -1561,16 +1558,16 @@
         <v>33</v>
       </c>
       <c r="G6" s="1">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I6" s="7">
-        <v>700000</v>
+        <v>2000</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:12">
@@ -1578,31 +1575,31 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>765000</v>
+        <v>1820000</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" s="1">
-        <v>7650</v>
+        <v>7000</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I7" s="7">
-        <v>700000</v>
+        <v>25000</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:12">
@@ -1610,7 +1607,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
@@ -1619,10 +1616,10 @@
       <c r="E8" s="2"/>
       <c r="J8" s="8"/>
       <c r="K8" s="1">
-        <v>1200000</v>
+        <v>24700000</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:12">
@@ -1630,7 +1627,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -1639,10 +1636,10 @@
       <c r="E9" s="2"/>
       <c r="J9" s="8"/>
       <c r="K9" s="1">
-        <v>3500000</v>
+        <v>74100000</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:12">
@@ -1650,7 +1647,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -1659,10 +1656,10 @@
       <c r="E10" s="2"/>
       <c r="J10" s="8"/>
       <c r="K10" s="1">
-        <v>5800000</v>
+        <v>123500000</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:12">
@@ -1670,7 +1667,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1679,10 +1676,10 @@
       <c r="E11" s="2"/>
       <c r="J11" s="8"/>
       <c r="K11" s="1">
-        <v>9200000</v>
+        <v>197600000</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:12">
@@ -1690,7 +1687,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -1699,10 +1696,10 @@
       <c r="E12" s="2"/>
       <c r="J12" s="8"/>
       <c r="K12" s="1">
-        <v>12700000</v>
+        <v>271700000</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:12">
@@ -1710,7 +1707,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -1719,10 +1716,10 @@
       <c r="E13" s="2"/>
       <c r="J13" s="8"/>
       <c r="K13" s="1">
-        <v>17300000</v>
+        <v>345800000</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:12">
@@ -1730,7 +1727,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1738,10 +1735,10 @@
       <c r="D14" s="1"/>
       <c r="J14" s="8"/>
       <c r="K14" s="1">
-        <v>21900000</v>
+        <v>419800000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:12">
@@ -1749,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -1757,10 +1754,10 @@
       <c r="D15" s="1"/>
       <c r="J15" s="8"/>
       <c r="K15" s="1">
-        <v>27600000</v>
+        <v>518600000</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:12">
@@ -1768,7 +1765,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" s="1">
         <v>4</v>
@@ -1776,10 +1773,10 @@
       <c r="D16" s="1"/>
       <c r="J16" s="8"/>
       <c r="K16" s="1">
-        <v>33400000</v>
+        <v>617400000</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:12">
@@ -1787,7 +1784,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
@@ -1795,10 +1792,10 @@
       <c r="D17" s="1"/>
       <c r="J17" s="8"/>
       <c r="K17" s="1">
-        <v>40300000</v>
+        <v>716200000</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:12">
@@ -1814,10 +1811,10 @@
       <c r="D18" s="1"/>
       <c r="J18" s="8"/>
       <c r="K18" s="1">
-        <v>47200000</v>
+        <v>814900000</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:12">
@@ -1833,10 +1830,10 @@
       <c r="D19" s="1"/>
       <c r="J19" s="8"/>
       <c r="K19" s="1">
-        <v>56400000</v>
+        <v>913700000</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:12">

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -98,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -121,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -143,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="61">
   <si>
     <t>序列ID</t>
   </si>
@@ -193,6 +193,9 @@
     <t>所占总奖池比例万分比</t>
   </si>
   <si>
+    <t>实际中奖比例：奖金万分比_权重|……</t>
+  </si>
+  <si>
     <t>固定金额奖励：次数下限_次数上限（左闭右开）_玩家中奖万分比概率|</t>
   </si>
   <si>
@@ -235,6 +238,9 @@
     <t>distribution</t>
   </si>
   <si>
+    <t>actualWinning</t>
+  </si>
+  <si>
     <t>weightQuota</t>
   </si>
   <si>
@@ -259,6 +265,9 @@
     <t>1_50_0|50_999999_280</t>
   </si>
   <si>
+    <t>100_50|300_50</t>
+  </si>
+  <si>
     <t>0_999999_1500</t>
   </si>
   <si>
@@ -274,6 +283,9 @@
     <t>1_12_0|12_999999_150</t>
   </si>
   <si>
+    <t>200_50|600_50</t>
+  </si>
+  <si>
     <t>0_999999_1000</t>
   </si>
   <si>
@@ -287,6 +299,9 @@
   </si>
   <si>
     <t>1_4_0|4_999999_50</t>
+  </si>
+  <si>
+    <t>400_50|1200_50</t>
   </si>
   <si>
     <t>0_999999_500</t>
@@ -1369,7 +1384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="3" customWidth="1"/>
@@ -1379,15 +1394,16 @@
     <col min="5" max="5" width="15.375" style="3" customWidth="1"/>
     <col min="6" max="6" width="44.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.25" style="3" customWidth="1"/>
-    <col min="8" max="8" width="44" style="3" customWidth="1"/>
-    <col min="9" max="9" width="20.375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="61.625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="17.5" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="3"/>
+    <col min="8" max="8" width="33.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="44" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="61.625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="17.5" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1409,109 +1425,118 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="H3" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="I3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="K3" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="K4" s="4"/>
       <c r="L4" s="4"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:12">
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:13">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
@@ -1520,30 +1545,33 @@
         <v>260000</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
         <v>1000</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="7">
+        <v>31</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="7">
         <v>500</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:12">
+      <c r="K5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:13">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C6" s="1">
         <v>2</v>
@@ -1552,30 +1580,33 @@
         <v>520000</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G6" s="1">
         <v>2000</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="7">
+        <v>37</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="7">
         <v>2000</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:12">
+      <c r="K6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:13">
       <c r="A7" s="1">
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
@@ -1584,284 +1615,287 @@
         <v>1820000</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G7" s="1">
         <v>7000</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="7">
+        <v>43</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="7">
         <v>25000</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:12">
+      <c r="K7" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:13">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="2"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="1">
+      <c r="K8" s="8"/>
+      <c r="L8" s="1">
         <v>24700000</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:12">
+      <c r="M8" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:13">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="2"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="1">
+      <c r="K9" s="8"/>
+      <c r="L9" s="1">
         <v>74100000</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:12">
+      <c r="M9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:13">
       <c r="A10" s="1">
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="2"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="1">
+      <c r="K10" s="8"/>
+      <c r="L10" s="1">
         <v>123500000</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:12">
+      <c r="M10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:13">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="2"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="1">
+      <c r="K11" s="8"/>
+      <c r="L11" s="1">
         <v>197600000</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:12">
+      <c r="M11" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:13">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="1">
+      <c r="K12" s="8"/>
+      <c r="L12" s="1">
         <v>271700000</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:12">
+      <c r="M12" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:13">
       <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="1">
+      <c r="K13" s="8"/>
+      <c r="L13" s="1">
         <v>345800000</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:12">
+      <c r="M13" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:13">
       <c r="A14" s="1">
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="1">
+      <c r="K14" s="8"/>
+      <c r="L14" s="1">
         <v>419800000</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:12">
+      <c r="M14" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:13">
       <c r="A15" s="1">
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="1">
+      <c r="K15" s="8"/>
+      <c r="L15" s="1">
         <v>518600000</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:12">
+      <c r="M15" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:13">
       <c r="A16" s="1">
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="1">
+      <c r="K16" s="8"/>
+      <c r="L16" s="1">
         <v>617400000</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:12">
+      <c r="M16" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:13">
       <c r="A17" s="1">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="1">
+      <c r="K17" s="8"/>
+      <c r="L17" s="1">
         <v>716200000</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:12">
+      <c r="M17" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:13">
       <c r="A18" s="1">
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="1">
+      <c r="K18" s="8"/>
+      <c r="L18" s="1">
         <v>814900000</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:12">
+      <c r="M18" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:13">
       <c r="A19" s="1">
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="1"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="1">
+      <c r="K19" s="8"/>
+      <c r="L19" s="1">
         <v>913700000</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="E20" s="1"/>
-      <c r="J20"/>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="K20"/>
+    </row>
+    <row r="21" spans="1:13">
       <c r="E21" s="1"/>
-      <c r="J21"/>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="K21"/>
+    </row>
+    <row r="22" spans="1:13">
       <c r="E22" s="1"/>
-      <c r="J22"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="J23"/>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="J24"/>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="J25"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="J26"/>
+      <c r="K22"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="K23"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="K24"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="K25"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="K26"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L2">
+  <conditionalFormatting sqref="M2">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD($B2,2)=1</formula>
     </cfRule>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -265,7 +265,7 @@
     <t>1_50_0|50_999999_280</t>
   </si>
   <si>
-    <t>100_50|300_50</t>
+    <t>200_60|300_30|500_10</t>
   </si>
   <si>
     <t>0_999999_1500</t>
@@ -283,7 +283,7 @@
     <t>1_12_0|12_999999_150</t>
   </si>
   <si>
-    <t>200_50|600_50</t>
+    <t>400_60|600_30|1000_10</t>
   </si>
   <si>
     <t>0_999999_1000</t>
@@ -301,7 +301,7 @@
     <t>1_4_0|4_999999_50</t>
   </si>
   <si>
-    <t>400_50|1200_50</t>
+    <t>1000_60|2000_30|4000_10</t>
   </si>
   <si>
     <t>0_999999_500</t>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -265,13 +265,13 @@
     <t>1_50_0|50_999999_280</t>
   </si>
   <si>
-    <t>200_60|300_30|500_10</t>
-  </si>
-  <si>
-    <t>0_999999_1500</t>
-  </si>
-  <si>
-    <t>0_12_1200_3600_1180|12_24_600_3600_2360</t>
+    <t>200_60|300_30|500_10|1000_1</t>
+  </si>
+  <si>
+    <t>0_999999_7500</t>
+  </si>
+  <si>
+    <t>0_12_1200_3600_1200|12_24_600_3600_1200</t>
   </si>
   <si>
     <t>银</t>
@@ -283,13 +283,13 @@
     <t>1_12_0|12_999999_150</t>
   </si>
   <si>
-    <t>400_60|600_30|1000_10</t>
-  </si>
-  <si>
-    <t>0_999999_1000</t>
-  </si>
-  <si>
-    <t>0_12_1200_4800_546|12_24_600_4800_1092</t>
+    <t>400_60|600_30|1000_10|2000_1</t>
+  </si>
+  <si>
+    <t>0_999999_5000</t>
+  </si>
+  <si>
+    <t>0_12_1200_4800_600|12_24_600_4800_600</t>
   </si>
   <si>
     <t>金</t>
@@ -298,16 +298,16 @@
     <t>1022501_15</t>
   </si>
   <si>
-    <t>1_4_0|4_999999_50</t>
-  </si>
-  <si>
-    <t>1000_60|2000_30|4000_10</t>
-  </si>
-  <si>
-    <t>0_999999_500</t>
-  </si>
-  <si>
-    <t>0_12_1200_7200_382|12_24_600_7200_764</t>
+    <t>1_3_0|3_999999_50</t>
+  </si>
+  <si>
+    <t>1000_60|2000_30|4000_10|7000_1</t>
+  </si>
+  <si>
+    <t>0_999999_2500</t>
+  </si>
+  <si>
+    <t>0_12_1200_7200_100|12_24_600_7200_100</t>
   </si>
   <si>
     <t>阶段奖励1</t>
@@ -1395,7 +1395,7 @@
     <col min="6" max="6" width="44.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="33.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="44" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.0333333333333" style="3" customWidth="1"/>
     <col min="10" max="10" width="20.375" style="3" customWidth="1"/>
     <col min="11" max="11" width="61.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="14.625" style="3" customWidth="1"/>
@@ -1542,7 +1542,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>260000</v>
+        <v>300000</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>29</v>
@@ -1560,7 +1560,7 @@
         <v>32</v>
       </c>
       <c r="J5" s="7">
-        <v>500</v>
+        <v>3900</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>33</v>
@@ -1577,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>520000</v>
+        <v>600000</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>35</v>
@@ -1595,7 +1595,7 @@
         <v>38</v>
       </c>
       <c r="J6" s="7">
-        <v>2000</v>
+        <v>15600</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>39</v>
@@ -1612,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>1820000</v>
+        <v>2100000</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>41</v>
@@ -1630,7 +1630,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="7">
-        <v>25000</v>
+        <v>58400</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>45</v>
@@ -1650,7 +1650,7 @@
       <c r="E8" s="2"/>
       <c r="K8" s="8"/>
       <c r="L8" s="1">
-        <v>24700000</v>
+        <v>1900000</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>47</v>
@@ -1670,7 +1670,7 @@
       <c r="E9" s="2"/>
       <c r="K9" s="8"/>
       <c r="L9" s="1">
-        <v>74100000</v>
+        <v>5700000</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>49</v>
@@ -1690,7 +1690,7 @@
       <c r="E10" s="2"/>
       <c r="K10" s="8"/>
       <c r="L10" s="1">
-        <v>123500000</v>
+        <v>9500000</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>49</v>
@@ -1710,7 +1710,7 @@
       <c r="E11" s="2"/>
       <c r="K11" s="8"/>
       <c r="L11" s="1">
-        <v>197600000</v>
+        <v>15100000</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>41</v>
@@ -1730,7 +1730,7 @@
       <c r="E12" s="2"/>
       <c r="K12" s="8"/>
       <c r="L12" s="1">
-        <v>271700000</v>
+        <v>20800000</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>41</v>
@@ -1750,7 +1750,7 @@
       <c r="E13" s="2"/>
       <c r="K13" s="8"/>
       <c r="L13" s="1">
-        <v>345800000</v>
+        <v>26500000</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>41</v>
@@ -1769,7 +1769,7 @@
       <c r="D14" s="1"/>
       <c r="K14" s="8"/>
       <c r="L14" s="1">
-        <v>419800000</v>
+        <v>32100000</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>41</v>
@@ -1788,7 +1788,7 @@
       <c r="D15" s="1"/>
       <c r="K15" s="8"/>
       <c r="L15" s="1">
-        <v>518600000</v>
+        <v>39700000</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>56</v>
@@ -1807,7 +1807,7 @@
       <c r="D16" s="1"/>
       <c r="K16" s="8"/>
       <c r="L16" s="1">
-        <v>617400000</v>
+        <v>47200000</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>56</v>
@@ -1826,7 +1826,7 @@
       <c r="D17" s="1"/>
       <c r="K17" s="8"/>
       <c r="L17" s="1">
-        <v>716200000</v>
+        <v>54800000</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>56</v>
@@ -1845,7 +1845,7 @@
       <c r="D18" s="1"/>
       <c r="K18" s="8"/>
       <c r="L18" s="1">
-        <v>814900000</v>
+        <v>62300000</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>56</v>
@@ -1864,7 +1864,7 @@
       <c r="D19" s="1"/>
       <c r="K19" s="8"/>
       <c r="L19" s="1">
-        <v>913700000</v>
+        <v>69900000</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>56</v>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -265,13 +265,13 @@
     <t>1_50_0|50_999999_280</t>
   </si>
   <si>
-    <t>200_60|300_30|500_10|1000_1</t>
-  </si>
-  <si>
-    <t>0_999999_7500</t>
-  </si>
-  <si>
-    <t>0_12_1200_3600_1200|12_24_600_3600_1200</t>
+    <t>200_60|300_30|500_10</t>
+  </si>
+  <si>
+    <t>0_999999_1500</t>
+  </si>
+  <si>
+    <t>0_12_1200_3600_1180|12_24_600_3600_2360</t>
   </si>
   <si>
     <t>银</t>
@@ -283,13 +283,13 @@
     <t>1_12_0|12_999999_150</t>
   </si>
   <si>
-    <t>400_60|600_30|1000_10|2000_1</t>
-  </si>
-  <si>
-    <t>0_999999_5000</t>
-  </si>
-  <si>
-    <t>0_12_1200_4800_600|12_24_600_4800_600</t>
+    <t>400_60|600_30|1000_10</t>
+  </si>
+  <si>
+    <t>0_999999_1000</t>
+  </si>
+  <si>
+    <t>0_12_1200_4800_546|12_24_600_4800_1092</t>
   </si>
   <si>
     <t>金</t>
@@ -298,16 +298,16 @@
     <t>1022501_15</t>
   </si>
   <si>
-    <t>1_3_0|3_999999_50</t>
-  </si>
-  <si>
-    <t>1000_60|2000_30|4000_10|7000_1</t>
-  </si>
-  <si>
-    <t>0_999999_2500</t>
-  </si>
-  <si>
-    <t>0_12_1200_7200_100|12_24_600_7200_100</t>
+    <t>1_4_0|4_999999_50</t>
+  </si>
+  <si>
+    <t>1000_60|2000_30|4000_10</t>
+  </si>
+  <si>
+    <t>0_999999_500</t>
+  </si>
+  <si>
+    <t>0_12_1200_7200_382|12_24_600_7200_764</t>
   </si>
   <si>
     <t>阶段奖励1</t>
@@ -1395,7 +1395,7 @@
     <col min="6" max="6" width="44.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="33.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="18.0333333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="44" style="3" customWidth="1"/>
     <col min="10" max="10" width="20.375" style="3" customWidth="1"/>
     <col min="11" max="11" width="61.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="14.625" style="3" customWidth="1"/>
@@ -1542,7 +1542,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>300000</v>
+        <v>260000</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>29</v>
@@ -1560,7 +1560,7 @@
         <v>32</v>
       </c>
       <c r="J5" s="7">
-        <v>3900</v>
+        <v>500</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>33</v>
@@ -1577,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>600000</v>
+        <v>520000</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>35</v>
@@ -1595,7 +1595,7 @@
         <v>38</v>
       </c>
       <c r="J6" s="7">
-        <v>15600</v>
+        <v>2000</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>39</v>
@@ -1612,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>2100000</v>
+        <v>1820000</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>41</v>
@@ -1630,7 +1630,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="7">
-        <v>58400</v>
+        <v>25000</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>45</v>
@@ -1650,7 +1650,7 @@
       <c r="E8" s="2"/>
       <c r="K8" s="8"/>
       <c r="L8" s="1">
-        <v>1900000</v>
+        <v>24700000</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>47</v>
@@ -1670,7 +1670,7 @@
       <c r="E9" s="2"/>
       <c r="K9" s="8"/>
       <c r="L9" s="1">
-        <v>5700000</v>
+        <v>74100000</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>49</v>
@@ -1690,7 +1690,7 @@
       <c r="E10" s="2"/>
       <c r="K10" s="8"/>
       <c r="L10" s="1">
-        <v>9500000</v>
+        <v>123500000</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>49</v>
@@ -1710,7 +1710,7 @@
       <c r="E11" s="2"/>
       <c r="K11" s="8"/>
       <c r="L11" s="1">
-        <v>15100000</v>
+        <v>197600000</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>41</v>
@@ -1730,7 +1730,7 @@
       <c r="E12" s="2"/>
       <c r="K12" s="8"/>
       <c r="L12" s="1">
-        <v>20800000</v>
+        <v>271700000</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>41</v>
@@ -1750,7 +1750,7 @@
       <c r="E13" s="2"/>
       <c r="K13" s="8"/>
       <c r="L13" s="1">
-        <v>26500000</v>
+        <v>345800000</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>41</v>
@@ -1769,7 +1769,7 @@
       <c r="D14" s="1"/>
       <c r="K14" s="8"/>
       <c r="L14" s="1">
-        <v>32100000</v>
+        <v>419800000</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>41</v>
@@ -1788,7 +1788,7 @@
       <c r="D15" s="1"/>
       <c r="K15" s="8"/>
       <c r="L15" s="1">
-        <v>39700000</v>
+        <v>518600000</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>56</v>
@@ -1807,7 +1807,7 @@
       <c r="D16" s="1"/>
       <c r="K16" s="8"/>
       <c r="L16" s="1">
-        <v>47200000</v>
+        <v>617400000</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>56</v>
@@ -1826,7 +1826,7 @@
       <c r="D17" s="1"/>
       <c r="K17" s="8"/>
       <c r="L17" s="1">
-        <v>54800000</v>
+        <v>716200000</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>56</v>
@@ -1845,7 +1845,7 @@
       <c r="D18" s="1"/>
       <c r="K18" s="8"/>
       <c r="L18" s="1">
-        <v>62300000</v>
+        <v>814900000</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>56</v>
@@ -1864,7 +1864,7 @@
       <c r="D19" s="1"/>
       <c r="K19" s="8"/>
       <c r="L19" s="1">
-        <v>69900000</v>
+        <v>913700000</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>56</v>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -1560,7 +1560,7 @@
         <v>32</v>
       </c>
       <c r="J5" s="7">
-        <v>3900</v>
+        <v>6500</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>33</v>
@@ -1595,7 +1595,7 @@
         <v>38</v>
       </c>
       <c r="J6" s="7">
-        <v>15600</v>
+        <v>25900</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>39</v>
@@ -1630,7 +1630,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="7">
-        <v>58400</v>
+        <v>97300</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>45</v>
@@ -1650,7 +1650,7 @@
       <c r="E8" s="2"/>
       <c r="K8" s="8"/>
       <c r="L8" s="1">
-        <v>1900000</v>
+        <v>1100000</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>47</v>
@@ -1670,7 +1670,7 @@
       <c r="E9" s="2"/>
       <c r="K9" s="8"/>
       <c r="L9" s="1">
-        <v>5700000</v>
+        <v>3300000</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>49</v>
@@ -1690,7 +1690,7 @@
       <c r="E10" s="2"/>
       <c r="K10" s="8"/>
       <c r="L10" s="1">
-        <v>9500000</v>
+        <v>5400000</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>49</v>
@@ -1710,7 +1710,7 @@
       <c r="E11" s="2"/>
       <c r="K11" s="8"/>
       <c r="L11" s="1">
-        <v>15100000</v>
+        <v>8600000</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>41</v>
@@ -1730,7 +1730,7 @@
       <c r="E12" s="2"/>
       <c r="K12" s="8"/>
       <c r="L12" s="1">
-        <v>20800000</v>
+        <v>11900000</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>41</v>
@@ -1750,7 +1750,7 @@
       <c r="E13" s="2"/>
       <c r="K13" s="8"/>
       <c r="L13" s="1">
-        <v>26500000</v>
+        <v>15100000</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>41</v>
@@ -1769,7 +1769,7 @@
       <c r="D14" s="1"/>
       <c r="K14" s="8"/>
       <c r="L14" s="1">
-        <v>32100000</v>
+        <v>18300000</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>41</v>
@@ -1788,7 +1788,7 @@
       <c r="D15" s="1"/>
       <c r="K15" s="8"/>
       <c r="L15" s="1">
-        <v>39700000</v>
+        <v>22600000</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>56</v>
@@ -1807,7 +1807,7 @@
       <c r="D16" s="1"/>
       <c r="K16" s="8"/>
       <c r="L16" s="1">
-        <v>47200000</v>
+        <v>26900000</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>56</v>
@@ -1826,7 +1826,7 @@
       <c r="D17" s="1"/>
       <c r="K17" s="8"/>
       <c r="L17" s="1">
-        <v>54800000</v>
+        <v>31200000</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>56</v>
@@ -1845,7 +1845,7 @@
       <c r="D18" s="1"/>
       <c r="K18" s="8"/>
       <c r="L18" s="1">
-        <v>62300000</v>
+        <v>35500000</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>56</v>
@@ -1864,7 +1864,7 @@
       <c r="D19" s="1"/>
       <c r="K19" s="8"/>
       <c r="L19" s="1">
-        <v>69900000</v>
+        <v>39800000</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>56</v>

--- a/table/resources/sample/CashCow.xlsx
+++ b/table/resources/sample/CashCow.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="cashcow" sheetId="1" r:id="rId1"/>
@@ -265,13 +265,13 @@
     <t>1_50_0|50_999999_280</t>
   </si>
   <si>
-    <t>200_60|300_30|500_10</t>
-  </si>
-  <si>
-    <t>0_999999_1500</t>
-  </si>
-  <si>
-    <t>0_12_1200_3600_1180|12_24_600_3600_2360</t>
+    <t>200_60|300_30|500_10|1000_1</t>
+  </si>
+  <si>
+    <t>0_999999_7500</t>
+  </si>
+  <si>
+    <t>0_12_1200_3600_1200|12_24_600_3600_1200</t>
   </si>
   <si>
     <t>银</t>
@@ -283,13 +283,13 @@
     <t>1_12_0|12_999999_150</t>
   </si>
   <si>
-    <t>400_60|600_30|1000_10</t>
-  </si>
-  <si>
-    <t>0_999999_1000</t>
-  </si>
-  <si>
-    <t>0_12_1200_4800_546|12_24_600_4800_1092</t>
+    <t>400_60|600_30|1000_10|2000_1</t>
+  </si>
+  <si>
+    <t>0_999999_5000</t>
+  </si>
+  <si>
+    <t>0_12_1200_4800_600|12_24_600_4800_600</t>
   </si>
   <si>
     <t>金</t>
@@ -298,16 +298,16 @@
     <t>1022501_15</t>
   </si>
   <si>
-    <t>1_4_0|4_999999_50</t>
-  </si>
-  <si>
-    <t>1000_60|2000_30|4000_10</t>
-  </si>
-  <si>
-    <t>0_999999_500</t>
-  </si>
-  <si>
-    <t>0_12_1200_7200_382|12_24_600_7200_764</t>
+    <t>1_3_0|3_999999_50</t>
+  </si>
+  <si>
+    <t>1000_60|2000_30|4000_10|7000_1</t>
+  </si>
+  <si>
+    <t>0_999999_2500</t>
+  </si>
+  <si>
+    <t>0_12_1200_7200_100|12_24_600_7200_100</t>
   </si>
   <si>
     <t>阶段奖励1</t>
@@ -1395,7 +1395,7 @@
     <col min="6" max="6" width="44.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="33.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="44" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.0333333333333" style="3" customWidth="1"/>
     <col min="10" max="10" width="20.375" style="3" customWidth="1"/>
     <col min="11" max="11" width="61.625" style="3" customWidth="1"/>
     <col min="12" max="12" width="14.625" style="3" customWidth="1"/>
@@ -1542,7 +1542,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>260000</v>
+        <v>300000</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>29</v>
@@ -1560,7 +1560,7 @@
         <v>32</v>
       </c>
       <c r="J5" s="7">
-        <v>500</v>
+        <v>6500</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>33</v>
@@ -1577,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>520000</v>
+        <v>600000</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>35</v>
@@ -1595,7 +1595,7 @@
         <v>38</v>
       </c>
       <c r="J6" s="7">
-        <v>2000</v>
+        <v>25900</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>39</v>
@@ -1612,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>1820000</v>
+        <v>2100000</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>41</v>
@@ -1630,7 +1630,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="7">
-        <v>25000</v>
+        <v>97300</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>45</v>
@@ -1650,7 +1650,7 @@
       <c r="E8" s="2"/>
       <c r="K8" s="8"/>
       <c r="L8" s="1">
-        <v>24700000</v>
+        <v>1100000</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>47</v>
@@ -1670,7 +1670,7 @@
       <c r="E9" s="2"/>
       <c r="K9" s="8"/>
       <c r="L9" s="1">
-        <v>74100000</v>
+        <v>3300000</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>49</v>
@@ -1690,7 +1690,7 @@
       <c r="E10" s="2"/>
       <c r="K10" s="8"/>
       <c r="L10" s="1">
-        <v>123500000</v>
+        <v>5400000</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>49</v>
@@ -1710,7 +1710,7 @@
       <c r="E11" s="2"/>
       <c r="K11" s="8"/>
       <c r="L11" s="1">
-        <v>197600000</v>
+        <v>8600000</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>41</v>
@@ -1730,7 +1730,7 @@
       <c r="E12" s="2"/>
       <c r="K12" s="8"/>
       <c r="L12" s="1">
-        <v>271700000</v>
+        <v>11900000</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>41</v>
@@ -1750,7 +1750,7 @@
       <c r="E13" s="2"/>
       <c r="K13" s="8"/>
       <c r="L13" s="1">
-        <v>345800000</v>
+        <v>15100000</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>41</v>
@@ -1769,7 +1769,7 @@
       <c r="D14" s="1"/>
       <c r="K14" s="8"/>
       <c r="L14" s="1">
-        <v>419800000</v>
+        <v>18300000</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>41</v>
@@ -1788,7 +1788,7 @@
       <c r="D15" s="1"/>
       <c r="K15" s="8"/>
       <c r="L15" s="1">
-        <v>518600000</v>
+        <v>22600000</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>56</v>
@@ -1807,7 +1807,7 @@
       <c r="D16" s="1"/>
       <c r="K16" s="8"/>
       <c r="L16" s="1">
-        <v>617400000</v>
+        <v>26900000</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>56</v>
@@ -1826,7 +1826,7 @@
       <c r="D17" s="1"/>
       <c r="K17" s="8"/>
       <c r="L17" s="1">
-        <v>716200000</v>
+        <v>31200000</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>56</v>
@@ -1845,7 +1845,7 @@
       <c r="D18" s="1"/>
       <c r="K18" s="8"/>
       <c r="L18" s="1">
-        <v>814900000</v>
+        <v>35500000</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>56</v>
@@ -1864,7 +1864,7 @@
       <c r="D19" s="1"/>
       <c r="K19" s="8"/>
       <c r="L19" s="1">
-        <v>913700000</v>
+        <v>39800000</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>56</v>
